--- a/docs/CodeSystem-BRRegistroOrigem.xlsx
+++ b/docs/CodeSystem-BRRegistroOrigem.xlsx
@@ -141,7 +141,7 @@
     <t>01</t>
   </si>
   <si>
-    <t>Registro anterior/Transcrição de caderneta</t>
+    <t>Transcrição de caderneta</t>
   </si>
   <si>
     <t>02</t>
